--- a/forms/trg/Formulir_TRG_cnrm.xlsx
+++ b/forms/trg/Formulir_TRG_cnrm.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Sawedi Muhammad, M.Sc</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1111,7 +1115,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1144,7 +1148,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
